--- a/artfynd/A 10627-2023 artfynd.xlsx
+++ b/artfynd/A 10627-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 10627-2023 artfynd.xlsx
+++ b/artfynd/A 10627-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107312697</v>
+        <v>108361156</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,45 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvarntjärn_spjuttjärn Kall-Rör, Jmt</t>
+          <t>Konäs, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>406517.449269623</v>
+        <v>406745</v>
       </c>
       <c r="R2" t="n">
-        <v>7049204.236128742</v>
+        <v>7049401</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2023-03-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>107312685</v>
+        <v>108361157</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,45 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kvarntjärn_spjuttjärn Kall-Rör, Jmt</t>
+          <t>Konäs, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>406788.8871734683</v>
+        <v>406701</v>
       </c>
       <c r="R3" t="n">
-        <v>7049171.735225605</v>
+        <v>7049432</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,27 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2023-03-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107312692</v>
+        <v>98332809</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -965,17 +904,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kvarntjärn_spjuttjärn Kall-Rör, Jmt</t>
+          <t>Kvällsbacken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>406732.6134001759</v>
+        <v>406322</v>
       </c>
       <c r="R4" t="n">
-        <v>7049353.991318868</v>
+        <v>7049470</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,27 +938,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-01-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-01-25</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,27 +963,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lisa Gideonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lisa Gideonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107312694</v>
+        <v>107312683</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,11 +1006,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1094,10 +1014,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>406559.7529358261</v>
+        <v>406847</v>
       </c>
       <c r="R5" t="n">
-        <v>7049260.964629905</v>
+        <v>7049469</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,26 +1047,21 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="b">
         <v>0</v>
@@ -1169,12 +1084,7 @@
         <v>107312684</v>
       </c>
       <c r="B6" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,10 +1120,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>406892.4214788026</v>
+        <v>406892</v>
       </c>
       <c r="R6" t="n">
-        <v>7049443.839178414</v>
+        <v>7049444</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,19 +1153,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1287,15 +1187,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107312690</v>
+        <v>107312685</v>
       </c>
       <c r="B7" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>406744.6198690116</v>
+        <v>406789</v>
       </c>
       <c r="R7" t="n">
-        <v>7049352.301143441</v>
+        <v>7049172</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1368,19 +1263,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1412,15 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>107312698</v>
+        <v>107312686</v>
       </c>
       <c r="B8" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1330,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1460,10 +1340,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406752.4515625906</v>
+        <v>406792</v>
       </c>
       <c r="R8" t="n">
-        <v>7049756.0542965</v>
+        <v>7049275</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1493,19 +1373,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1537,15 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>107312693</v>
+        <v>107312687</v>
       </c>
       <c r="B9" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,11 +1438,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1585,10 +1446,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>406640.3458545229</v>
+        <v>406786</v>
       </c>
       <c r="R9" t="n">
-        <v>7049298.730056676</v>
+        <v>7049306</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1618,19 +1479,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1662,15 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>107312703</v>
+        <v>107312688</v>
       </c>
       <c r="B10" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1698,11 +1544,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1710,10 +1552,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>406680.9914498601</v>
+        <v>406783</v>
       </c>
       <c r="R10" t="n">
-        <v>7050043.942084214</v>
+        <v>7049308</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1743,19 +1585,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1787,15 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>107312686</v>
+        <v>107312689</v>
       </c>
       <c r="B11" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1835,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>406791.4601000915</v>
+        <v>406765</v>
       </c>
       <c r="R11" t="n">
-        <v>7049274.672635309</v>
+        <v>7049331</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1868,19 +1695,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1912,15 +1729,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>107312702</v>
+        <v>107312690</v>
       </c>
       <c r="B12" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1960,10 +1772,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>406753.4352507558</v>
+        <v>406745</v>
       </c>
       <c r="R12" t="n">
-        <v>7049759.146506752</v>
+        <v>7049352</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1993,19 +1805,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2037,15 +1839,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>107312695</v>
+        <v>107312692</v>
       </c>
       <c r="B13" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2073,11 +1870,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2085,10 +1878,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>406563.1263167646</v>
+        <v>406732</v>
       </c>
       <c r="R13" t="n">
-        <v>7049239.014297043</v>
+        <v>7049354</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2118,19 +1911,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2162,15 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>107312688</v>
+        <v>107312693</v>
       </c>
       <c r="B14" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2198,7 +1976,11 @@
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2206,10 +1988,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406783.0451576257</v>
+        <v>406640</v>
       </c>
       <c r="R14" t="n">
-        <v>7049307.472649627</v>
+        <v>7049299</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2239,19 +2021,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2283,15 +2055,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>107312696</v>
+        <v>107312694</v>
       </c>
       <c r="B15" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2321,7 +2088,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2331,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>406527.7119940845</v>
+        <v>406560</v>
       </c>
       <c r="R15" t="n">
-        <v>7049173.609599844</v>
+        <v>7049261</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2364,31 +2131,16 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG15" t="b">
         <v>0</v>
@@ -2408,15 +2160,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>107312687</v>
+        <v>107312695</v>
       </c>
       <c r="B16" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2444,7 +2191,11 @@
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2452,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>406786.1158803605</v>
+        <v>406563</v>
       </c>
       <c r="R16" t="n">
-        <v>7049305.598841196</v>
+        <v>7049239</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2485,19 +2236,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2529,15 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>107312689</v>
+        <v>107312696</v>
       </c>
       <c r="B17" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2577,10 +2313,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>406764.9869476224</v>
+        <v>406528</v>
       </c>
       <c r="R17" t="n">
-        <v>7049331.190819862</v>
+        <v>7049173</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2610,19 +2346,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2654,15 +2380,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>107312683</v>
+        <v>107312697</v>
       </c>
       <c r="B18" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2690,7 +2411,11 @@
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2698,10 +2423,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406847.1499196285</v>
+        <v>406518</v>
       </c>
       <c r="R18" t="n">
-        <v>7049468.35343469</v>
+        <v>7049204</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2731,19 +2456,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2775,15 +2490,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>108361156</v>
+        <v>107312698</v>
       </c>
       <c r="B19" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2791,37 +2501,45 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Konäs, Jmt</t>
+          <t>Kvarntjärn_spjuttjärn Kall-Rör, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>406745.1528993626</v>
+        <v>406753</v>
       </c>
       <c r="R19" t="n">
-        <v>7049400.891019657</v>
+        <v>7049756</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2845,22 +2563,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-03-29</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-03-29</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2875,27 +2588,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>108361157</v>
+        <v>107312702</v>
       </c>
       <c r="B20" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2903,37 +2611,45 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Konäs, Jmt</t>
+          <t>Kvarntjärn_spjuttjärn Kall-Rör, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>406700.5110559111</v>
+        <v>406754</v>
       </c>
       <c r="R20" t="n">
-        <v>7049431.632058472</v>
+        <v>7049759</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2957,22 +2673,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-03-29</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-03-29</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-15</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2987,27 +2698,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>108361155</v>
+        <v>107312703</v>
       </c>
       <c r="B21" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3033,24 +2739,27 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Konäs, Jmt</t>
+          <t>Kvarntjärn_spjuttjärn Kall-Rör, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>406737.2432622412</v>
+        <v>406681</v>
       </c>
       <c r="R21" t="n">
-        <v>7049374.813850907</v>
+        <v>7050044</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3074,27 +2783,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-03-29</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-03-29</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-15</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3109,12 +2808,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3124,12 +2823,7 @@
         <v>108361153</v>
       </c>
       <c r="B22" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3166,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>406577.9152091565</v>
+        <v>406578</v>
       </c>
       <c r="R22" t="n">
-        <v>7049498.999574088</v>
+        <v>7049499</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3199,19 +2893,9 @@
           <t>2023-03-29</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-03-29</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3246,12 +2930,7 @@
         <v>108361154</v>
       </c>
       <c r="B23" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3288,10 +2967,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>406602.4986326799</v>
+        <v>406603</v>
       </c>
       <c r="R23" t="n">
-        <v>7049363.164307177</v>
+        <v>7049363</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3321,19 +3000,9 @@
           <t>2023-03-29</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-03-29</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3362,6 +3031,113 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>108361155</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Konäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>406737</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7049375</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-03-29</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-03-29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10627-2023 artfynd.xlsx
+++ b/artfynd/A 10627-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108361156</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108361157</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98332809</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312683</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312684</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312685</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1404,6 +1439,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312686</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1510,6 +1550,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312687</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1616,6 +1661,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312688</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1726,6 +1776,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312689</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1836,6 +1891,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312690</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1942,6 +2002,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312692</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2052,6 +2117,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312693</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2157,6 +2227,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312694</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2267,6 +2342,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312695</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2377,6 +2457,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312696</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2487,6 +2572,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312697</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2597,6 +2687,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312698</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2707,6 +2802,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312702</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2817,6 +2917,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312703</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2924,6 +3029,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108361153</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3031,6 +3141,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108361154</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3138,8 +3253,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108361155</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>